--- a/frontend/public/plantillas/facturas-recibidas.xlsx
+++ b/frontend/public/plantillas/facturas-recibidas.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">Fecha expedición</t>
   </si>
@@ -30,6 +30,12 @@
   </si>
   <si>
     <t xml:space="preserve">Cuota IVA soportada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo retención IRPF (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importe retenido IRPF</t>
   </si>
   <si>
     <t xml:space="preserve">Total factura</t>
@@ -126,6 +132,12 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -136,38 +148,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
